--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4148-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4148-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CCB0185-E501-42E2-A4B9-ADAA95CB455E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17700A12-9953-4313-8C6D-F728574AF204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{61C1DF3C-20B1-4876-A549-8F7B63DCD3BB}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{E1FCE51D-10F5-42ED-A865-3CDA3F9CB7EF}"/>
   </bookViews>
   <sheets>
     <sheet name="4148-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1475,25 +1475,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5463FFB-3044-43C6-853E-8CFBC42968EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F41460-1AE0-4201-B696-33DFFB07B5DB}">
   <dimension ref="A1:X28"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9.125" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1527,7 +1527,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1563,7 +1563,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1683,7 +1683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2022</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2021</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2020</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2019</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>5.39</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2018</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2017</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2016</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35" t="s">
         <v>46</v>
       </c>
